--- a/通讯录输出/资质升级_贵州_300条.xlsx
+++ b/通讯录输出/资质升级_贵州_300条.xlsx
@@ -178,6 +178,58 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
